--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MADERAS SORLI BENICARLO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MADERAS SORLI BENICARLO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>22.4369</v>
+        <v>44.0989</v>
       </c>
       <c r="E2" t="n">
-        <v>15.6874</v>
+        <v>30.8162</v>
       </c>
       <c r="F2" t="n">
-        <v>6.7494</v>
+        <v>13.2825</v>
       </c>
       <c r="G2" t="n">
         <v>22.6542</v>
@@ -610,13 +610,13 @@
         <v>54.8263</v>
       </c>
       <c r="S2" t="n">
-        <v>-20.2322</v>
+        <v>1.4299</v>
       </c>
       <c r="T2" t="n">
-        <v>-14.0149</v>
+        <v>1.1143</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.2174</v>
+        <v>0.3155000000000002</v>
       </c>
       <c r="V2" t="n">
         <v>20.4255</v>
@@ -643,13 +643,13 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>13.5862</v>
+        <v>7.645499999999998</v>
       </c>
       <c r="E3" t="n">
-        <v>22.3485</v>
+        <v>17.0564</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.7624</v>
+        <v>-9.411</v>
       </c>
       <c r="G3" t="n">
         <v>10.7777</v>
@@ -688,13 +688,13 @@
         <v>16.4273</v>
       </c>
       <c r="S3" t="n">
-        <v>11.3493</v>
+        <v>5.4086</v>
       </c>
       <c r="T3" t="n">
-        <v>10.9627</v>
+        <v>5.6706</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3869000000000001</v>
+        <v>-0.2618999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-5.0499</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>3.260799999999998</v>
+        <v>1.8169</v>
       </c>
       <c r="E4" t="n">
-        <v>8.144500000000001</v>
+        <v>-1.742600000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.884000000000001</v>
+        <v>3.5592</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.607099999999999</v>
+        <v>-17.1224</v>
       </c>
       <c r="H4" t="n">
-        <v>12.8517</v>
+        <v>-9.1347</v>
       </c>
       <c r="I4" t="n">
-        <v>-18.4585</v>
+        <v>-7.9876</v>
       </c>
       <c r="J4" t="n">
-        <v>22.4036</v>
+        <v>-7.7162</v>
       </c>
       <c r="K4" t="n">
-        <v>27.5636</v>
+        <v>-5.5826</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.160399999999999</v>
+        <v>-2.1337</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.0102</v>
+        <v>-9.4063</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.7122</v>
+        <v>-3.5521</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.2982</v>
+        <v>-5.8539</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.187</v>
+        <v>9.4458</v>
       </c>
       <c r="Q4" t="n">
-        <v>-54.6208</v>
+        <v>-6.981599999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>47.4341</v>
+        <v>16.4275</v>
       </c>
       <c r="S4" t="n">
-        <v>42.0039</v>
+        <v>0.3135999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>33.4103</v>
+        <v>-0.381</v>
       </c>
       <c r="U4" t="n">
-        <v>8.593400000000001</v>
+        <v>0.6949999999999998</v>
       </c>
       <c r="V4" t="n">
-        <v>-25.9493</v>
+        <v>9.1799</v>
       </c>
       <c r="W4" t="n">
-        <v>6.9518</v>
+        <v>13.3365</v>
       </c>
       <c r="X4" t="n">
-        <v>-32.9015</v>
+        <v>-4.1567</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>P. LLORACH CORNELLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0497</v>
+        <v>-3.8398</v>
       </c>
       <c r="E5" t="n">
-        <v>8.844199999999999</v>
+        <v>-2.2132</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.7946</v>
+        <v>-1.6266</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.3222</v>
+        <v>-1.0176</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.883</v>
+        <v>-0.8596999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.4393</v>
+        <v>-0.158</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6537</v>
+        <v>-0.1208</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8382</v>
+        <v>-0.0549</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8155</v>
+        <v>-0.0659</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.9757</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.7212</v>
+        <v>-0.8048</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.2545</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>-1.6428</v>
       </c>
       <c r="Q5" t="n">
-        <v>-12.9365</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>12.9365</v>
+        <v>0.4106</v>
       </c>
       <c r="S5" t="n">
-        <v>12.3516</v>
+        <v>-0.8911</v>
       </c>
       <c r="T5" t="n">
-        <v>11.9735</v>
+        <v>-0.03880000000000002</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3780999999999999</v>
+        <v>-0.8523000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9796</v>
+        <v>-0.2882</v>
       </c>
       <c r="W5" t="n">
-        <v>5.1538</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.1334</v>
+        <v>-0.2882</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>G. FOLLA-CISNEROS GIMENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0139</v>
+        <v>-4.1922</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.839600000000001</v>
+        <v>-0.1386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8254</v>
+        <v>-4.0536</v>
       </c>
       <c r="G6" t="n">
-        <v>-17.1224</v>
+        <v>-0.8614999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.1347</v>
+        <v>-1.0642</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.9876</v>
+        <v>0.2027</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.7162</v>
+        <v>0.059</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.5826</v>
+        <v>0.0195</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.1337</v>
+        <v>0.0395</v>
       </c>
       <c r="M6" t="n">
-        <v>-9.4063</v>
+        <v>-0.9204</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.5521</v>
+        <v>-1.0837</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.8539</v>
+        <v>0.1632</v>
       </c>
       <c r="P6" t="n">
-        <v>9.4458</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.981599999999999</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>16.4275</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.5172</v>
+        <v>-0.5414</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.478</v>
+        <v>-0.1976</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.0391</v>
+        <v>-0.3438</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1799</v>
+        <v>-2.9946</v>
       </c>
       <c r="W6" t="n">
-        <v>13.3365</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.1567</v>
+        <v>-2.9946</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. LLORACH CORNELLES</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.2334</v>
+        <v>-5.163500000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4882</v>
+        <v>-1.4717</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7451</v>
+        <v>-3.6919</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0176</v>
+        <v>-10.9725</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8596999999999999</v>
+        <v>-2.3123</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.158</v>
+        <v>-8.660299999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1208</v>
+        <v>-6.3086</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0549</v>
+        <v>-0.3988</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0659</v>
+        <v>-5.909800000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-4.6641</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8048</v>
+        <v>-1.9136</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-2.750400000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6428</v>
+        <v>4.5176</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>-3.696099999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4106</v>
+        <v>8.213800000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2848</v>
+        <v>-2.7856</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3138</v>
+        <v>-1.6166</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9708</v>
+        <v>-1.169</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2882</v>
+        <v>4.077100000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>10.1497</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2882</v>
+        <v>-6.0724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FOLLA-CISNEROS GIMENO</t>
+          <t>M. BETCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.486499999999999</v>
+        <v>-5.3503</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2045</v>
+        <v>2.1666</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2818</v>
+        <v>-7.516999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8614999999999999</v>
+        <v>0.1477000000000004</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0642</v>
+        <v>-3.2187</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2027</v>
+        <v>3.3666</v>
       </c>
       <c r="J8" t="n">
-        <v>0.059</v>
+        <v>4.761699999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0195</v>
+        <v>-0.03790000000000004</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>4.7996</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9204</v>
+        <v>-4.614</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0837</v>
+        <v>-3.1808</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1632</v>
+        <v>-1.433</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>0.8213</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.4908</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>4.3122</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8355999999999999</v>
+        <v>-2.1328</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2635</v>
+        <v>-0.8723</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5722</v>
+        <v>-1.2606</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.9946</v>
+        <v>-4.1868</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9946</v>
+        <v>-5.9547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BETCH</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.5317</v>
+        <v>-5.9566</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3026</v>
+        <v>0.1275000000000004</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.834300000000001</v>
+        <v>-6.084</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1477000000000004</v>
+        <v>-7.3222</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.2187</v>
+        <v>-4.883</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3666</v>
+        <v>-2.4393</v>
       </c>
       <c r="J9" t="n">
-        <v>4.761699999999999</v>
+        <v>4.6537</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.03790000000000004</v>
+        <v>2.8382</v>
       </c>
       <c r="L9" t="n">
-        <v>4.7996</v>
+        <v>1.8155</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.614</v>
+        <v>-11.9757</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1808</v>
+        <v>-7.7212</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.433</v>
+        <v>-4.2545</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8213</v>
+        <v>-1.665334536937735e-16</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4908</v>
+        <v>-12.9365</v>
       </c>
       <c r="R9" t="n">
-        <v>4.3122</v>
+        <v>12.9365</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.314</v>
+        <v>3.3453</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7362</v>
+        <v>3.2566</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5779</v>
+        <v>0.08869999999999986</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.1868</v>
+        <v>-1.9796</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7679</v>
+        <v>5.1538</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.9547</v>
+        <v>-7.1334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>M. BECHT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.448100000000001</v>
+        <v>-9.095799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3978999999999999</v>
+        <v>-8.824400000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.846299999999999</v>
+        <v>-0.2713</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.5517</v>
+        <v>-9.699300000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.2032</v>
+        <v>-3.7538</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.3487</v>
+        <v>-5.9455</v>
       </c>
       <c r="J10" t="n">
-        <v>7.663</v>
+        <v>-7.7305</v>
       </c>
       <c r="K10" t="n">
-        <v>2.650599999999999</v>
+        <v>0.4556000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>5.0122</v>
+        <v>-8.1861</v>
       </c>
       <c r="M10" t="n">
-        <v>-23.2144</v>
+        <v>-1.9686</v>
       </c>
       <c r="N10" t="n">
-        <v>-12.8537</v>
+        <v>-4.2093</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.361</v>
+        <v>2.2406</v>
       </c>
       <c r="P10" t="n">
-        <v>10.0616</v>
+        <v>3.9014</v>
       </c>
       <c r="Q10" t="n">
-        <v>-24.0249</v>
+        <v>-3.4907</v>
       </c>
       <c r="R10" t="n">
-        <v>34.0867</v>
+        <v>7.392300000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>12.3055</v>
+        <v>-2.1803</v>
       </c>
       <c r="T10" t="n">
-        <v>7.9618</v>
+        <v>-2.5578</v>
       </c>
       <c r="U10" t="n">
-        <v>4.3438</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-14.2637</v>
+        <v>-1.1178</v>
       </c>
       <c r="W10" t="n">
-        <v>8.798500000000001</v>
+        <v>4.9546</v>
       </c>
       <c r="X10" t="n">
-        <v>-23.0622</v>
+        <v>-6.0725</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.359100000000002</v>
+        <v>-13.963</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1608</v>
+        <v>-9.773299999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.198399999999999</v>
+        <v>-4.1897</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.9725</v>
+        <v>-27.7973</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3123</v>
+        <v>-8.7753</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.660299999999999</v>
+        <v>-19.0217</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.3086</v>
+        <v>-4.477</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3988</v>
+        <v>3.3557</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.909800000000001</v>
+        <v>-7.8324</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.6641</v>
+        <v>-23.3203</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9136</v>
+        <v>-12.1312</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.750400000000001</v>
+        <v>-11.1893</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5176</v>
+        <v>4.1071</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.696099999999999</v>
+        <v>-19.0967</v>
       </c>
       <c r="R11" t="n">
-        <v>8.213800000000001</v>
+        <v>23.2038</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.9813</v>
+        <v>4.3144</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.3057</v>
+        <v>4.5886</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6754</v>
+        <v>-0.2742999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>4.077100000000001</v>
+        <v>5.4129</v>
       </c>
       <c r="W11" t="n">
-        <v>10.1497</v>
+        <v>9.2113</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.0724</v>
+        <v>-3.7986</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BECHT</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.3532</v>
+        <v>-14.7761</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.2188</v>
+        <v>-2.5629</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1344</v>
+        <v>-12.2135</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.699300000000001</v>
+        <v>-8.556800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.7538</v>
+        <v>-11.5583</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.9455</v>
+        <v>3.0012</v>
       </c>
       <c r="J12" t="n">
-        <v>-7.7305</v>
+        <v>7.863300000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4556000000000001</v>
+        <v>-5.63</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.1861</v>
+        <v>13.4932</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9686</v>
+        <v>-16.4198</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.2093</v>
+        <v>-5.9282</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2406</v>
+        <v>-10.4921</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9014</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4907</v>
+        <v>-23.2036</v>
       </c>
       <c r="R12" t="n">
-        <v>7.392300000000001</v>
+        <v>21.3556</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.4376</v>
+        <v>0.7922999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.9521</v>
+        <v>2.6054</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4854999999999999</v>
+        <v>-1.8131</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1178</v>
+        <v>-5.163400000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>4.9546</v>
+        <v>10.1722</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.0725</v>
+        <v>-15.3357</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.0425</v>
+        <v>-14.9724</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5322</v>
+        <v>-4.582</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.5104</v>
+        <v>-10.3905</v>
       </c>
       <c r="G13" t="n">
         <v>-26.3477</v>
@@ -1468,13 +1468,13 @@
         <v>33.0602</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7761</v>
+        <v>2.8463</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6855</v>
+        <v>0.6357999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0904</v>
+        <v>2.2104</v>
       </c>
       <c r="V13" t="n">
         <v>-6.6663</v>
@@ -1501,13 +1501,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.4903</v>
+        <v>-15.2356</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.3071</v>
+        <v>-11.7485</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.1831</v>
+        <v>-3.487000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-19.6042</v>
@@ -1546,13 +1546,13 @@
         <v>22.5877</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9342999999999999</v>
+        <v>1.1888</v>
       </c>
       <c r="T14" t="n">
-        <v>2.369</v>
+        <v>1.9273</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4349</v>
+        <v>-0.7384999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-10.9892</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-18.619</v>
+        <v>-15.2367</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.1231</v>
+        <v>-5.269600000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.4958</v>
+        <v>-9.966799999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.556800000000001</v>
+        <v>-15.5517</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.5583</v>
+        <v>-10.2032</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0012</v>
+        <v>-5.3487</v>
       </c>
       <c r="J15" t="n">
-        <v>7.863300000000001</v>
+        <v>7.663</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.63</v>
+        <v>2.650599999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>13.4932</v>
+        <v>5.0122</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.4198</v>
+        <v>-23.2144</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.9282</v>
+        <v>-12.8537</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.4921</v>
+        <v>-10.361</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8481</v>
+        <v>10.0616</v>
       </c>
       <c r="Q15" t="n">
-        <v>-23.2036</v>
+        <v>-24.0249</v>
       </c>
       <c r="R15" t="n">
-        <v>21.3556</v>
+        <v>34.0867</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.0506</v>
+        <v>4.5171</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9550000000000004</v>
+        <v>2.2941</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.0956</v>
+        <v>2.2235</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.163400000000001</v>
+        <v>-14.2637</v>
       </c>
       <c r="W15" t="n">
-        <v>10.1722</v>
+        <v>8.798500000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.3357</v>
+        <v>-23.0622</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.1096</v>
+        <v>-20.8428</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.0474</v>
+        <v>-0.5500000000000012</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.0623</v>
+        <v>-20.2924</v>
       </c>
       <c r="G16" t="n">
-        <v>-27.7973</v>
+        <v>-14.3268</v>
       </c>
       <c r="H16" t="n">
-        <v>-8.7753</v>
+        <v>-8.7554</v>
       </c>
       <c r="I16" t="n">
-        <v>-19.0217</v>
+        <v>-5.5712</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.477</v>
+        <v>24.343</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3557</v>
+        <v>16.6395</v>
       </c>
       <c r="L16" t="n">
-        <v>-7.8324</v>
+        <v>7.7032</v>
       </c>
       <c r="M16" t="n">
-        <v>-23.3203</v>
+        <v>-38.6699</v>
       </c>
       <c r="N16" t="n">
-        <v>-12.1312</v>
+        <v>-25.3948</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.1893</v>
+        <v>-13.2747</v>
       </c>
       <c r="P16" t="n">
-        <v>4.1071</v>
+        <v>16.0165</v>
       </c>
       <c r="Q16" t="n">
-        <v>-19.0967</v>
+        <v>-23.8195</v>
       </c>
       <c r="R16" t="n">
-        <v>23.2038</v>
+        <v>39.8364</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.8317</v>
+        <v>-5.4711</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3152</v>
+        <v>-2.9953</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.1469</v>
+        <v>-2.4757</v>
       </c>
       <c r="V16" t="n">
-        <v>5.4129</v>
+        <v>-17.0615</v>
       </c>
       <c r="W16" t="n">
-        <v>9.2113</v>
+        <v>1.9216</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.7986</v>
+        <v>-18.9833</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-37.7873</v>
+        <v>-20.9639</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.4009</v>
+        <v>-11.6019</v>
       </c>
       <c r="F17" t="n">
-        <v>-24.3862</v>
+        <v>-9.362400000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-14.3268</v>
+        <v>-5.607099999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.7554</v>
+        <v>12.8517</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.5712</v>
+        <v>-18.4585</v>
       </c>
       <c r="J17" t="n">
-        <v>24.343</v>
+        <v>22.4036</v>
       </c>
       <c r="K17" t="n">
-        <v>16.6395</v>
+        <v>27.5636</v>
       </c>
       <c r="L17" t="n">
-        <v>7.7032</v>
+        <v>-5.160399999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-38.6699</v>
+        <v>-28.0102</v>
       </c>
       <c r="N17" t="n">
-        <v>-25.3948</v>
+        <v>-14.7122</v>
       </c>
       <c r="O17" t="n">
-        <v>-13.2747</v>
+        <v>-13.2982</v>
       </c>
       <c r="P17" t="n">
-        <v>16.0165</v>
+        <v>-7.187</v>
       </c>
       <c r="Q17" t="n">
-        <v>-23.8195</v>
+        <v>-54.6208</v>
       </c>
       <c r="R17" t="n">
-        <v>39.8364</v>
+        <v>47.4341</v>
       </c>
       <c r="S17" t="n">
-        <v>-22.4155</v>
+        <v>17.7792</v>
       </c>
       <c r="T17" t="n">
-        <v>-15.8462</v>
+        <v>13.6641</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.569100000000001</v>
+        <v>4.1153</v>
       </c>
       <c r="V17" t="n">
-        <v>-17.0615</v>
+        <v>-25.9493</v>
       </c>
       <c r="W17" t="n">
-        <v>1.9216</v>
+        <v>6.9518</v>
       </c>
       <c r="X17" t="n">
-        <v>-18.9833</v>
+        <v>-32.9015</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-48.8315</v>
+        <v>-29.1567</v>
       </c>
       <c r="E18" t="n">
-        <v>-39.5293</v>
+        <v>-26.2983</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.302399999999999</v>
+        <v>-2.8583</v>
       </c>
       <c r="G18" t="n">
         <v>-20.9527</v>
@@ -1858,13 +1858,13 @@
         <v>50.5141</v>
       </c>
       <c r="S18" t="n">
-        <v>-24.3752</v>
+        <v>-4.7005</v>
       </c>
       <c r="T18" t="n">
-        <v>-14.9127</v>
+        <v>-1.6821</v>
       </c>
       <c r="U18" t="n">
-        <v>-9.4628</v>
+        <v>-3.0186</v>
       </c>
       <c r="V18" t="n">
         <v>1.835500000000001</v>
@@ -1891,22 +1891,22 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-157.9725</v>
+        <v>-125.1841</v>
       </c>
       <c r="E19" t="n">
-        <v>-49.1268</v>
+        <v>-36.61030000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-108.8467</v>
+        <v>-88.57430000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-152.1602</v>
       </c>
       <c r="H19" t="n">
-        <v>-65.33540000000001</v>
+        <v>-65.33539999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-86.8245</v>
+        <v>-86.82449999999999</v>
       </c>
       <c r="J19" t="n">
         <v>149.3988</v>
@@ -1915,7 +1915,7 @@
         <v>112.7039</v>
       </c>
       <c r="L19" t="n">
-        <v>36.69400000000001</v>
+        <v>36.694</v>
       </c>
       <c r="M19" t="n">
         <v>-301.5572</v>
@@ -1927,7 +1927,7 @@
         <v>-123.5187</v>
       </c>
       <c r="P19" t="n">
-        <v>58.5216</v>
+        <v>58.52159999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-334.7062</v>
@@ -1936,13 +1936,13 @@
         <v>393.2304</v>
       </c>
       <c r="S19" t="n">
-        <v>-9.555000000000007</v>
+        <v>23.2327</v>
       </c>
       <c r="T19" t="n">
-        <v>12.89989999999999</v>
+        <v>25.4153</v>
       </c>
       <c r="U19" t="n">
-        <v>-22.455</v>
+        <v>-2.1819</v>
       </c>
       <c r="V19" t="n">
         <v>-54.7794</v>
